--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,48 +796,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130587517</v>
+        <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ekängen, Ekängen, Sm</t>
+          <t>Gamleby, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583327</v>
+        <v>583459</v>
       </c>
       <c r="R3" t="n">
-        <v>6419420</v>
+        <v>6418956</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,85 +886,83 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Louise Lundberg</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130587517</t>
+          <t>https://artportalen.se/Sighting/136684905</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16879101</v>
+        <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>9406</v>
+        <v>92126</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101246</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gamleby, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583638</v>
+        <v>583412</v>
       </c>
       <c r="R4" t="n">
-        <v>6418841</v>
+        <v>6418998</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,17 +986,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-06-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-06-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En 9-cm hane nästan drunknad i en vattentunna tillsammans med en hona. En 5-cm hane friflygande. Medobservatör: Björn Erlandsson</t>
+          <t>I den gamla tallen ( ca 75% levande) finns även minst ett bohål ( &lt;10 cm)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,75 +1005,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Karlsson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Stefan Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Ekoxeuppropet 2013</t>
-        </is>
-      </c>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16879101</t>
+          <t>https://artportalen.se/Sighting/136685543</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118861580</v>
+        <v>130587517</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Garpedansberget, Sm</t>
+          <t>Ekängen, Ekängen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583433</v>
+        <v>583327</v>
       </c>
       <c r="R5" t="n">
-        <v>6418625</v>
+        <v>6419420</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,12 +1094,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,27 +1124,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Louise Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118861580</t>
+          <t>https://artportalen.se/Sighting/130587517</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118861581</v>
+        <v>16879101</v>
       </c>
       <c r="B6" t="n">
-        <v>4988</v>
+        <v>9406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,45 +1152,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100307</v>
+        <v>101246</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blompraktbagge</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthaxia morio</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Garpedansberget, Sm</t>
+          <t>Gamleby, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583433</v>
+        <v>583638</v>
       </c>
       <c r="R6" t="n">
-        <v>6418625</v>
+        <v>6418841</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,12 +1220,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2013-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2013-06-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En 9-cm hane nästan drunknad i en vattentunna tillsammans med en hona. En 5-cm hane friflygande. Medobservatör: Björn Erlandsson</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,84 +1245,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Stefan Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Stefan Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2013</t>
+        </is>
+      </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118861581</t>
+          <t>https://artportalen.se/Sighting/16879101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13582134</v>
+        <v>118861580</v>
       </c>
       <c r="B7" t="n">
-        <v>9406</v>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101246</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gamleby,, Sm</t>
+          <t>Garpedansberget, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583548</v>
+        <v>583433</v>
       </c>
       <c r="R7" t="n">
-        <v>6418595</v>
+        <v>6418625</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,12 +1331,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2008-07-27</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2008-07-27</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,27 +1351,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13582134</t>
+          <t>https://artportalen.se/Sighting/118861580</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98324657</v>
+        <v>118861581</v>
       </c>
       <c r="B8" t="n">
-        <v>9406</v>
+        <v>4988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,43 +1379,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101246</v>
+        <v>100307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Blompraktbagge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Anthaxia morio</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Garpedansvägen 15, Sm</t>
+          <t>Garpedansberget, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583554</v>
+        <v>583433</v>
       </c>
       <c r="R8" t="n">
-        <v>6418590</v>
+        <v>6418625</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1440,17 +1441,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ekoxeuppropet 2020. 1 levande resten döende</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,28 +1461,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Ekoxeuppropet 2020</t>
-        </is>
-      </c>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98324657</t>
+          <t>https://artportalen.se/Sighting/118861581</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>98324354</v>
+        <v>13582134</v>
       </c>
       <c r="B9" t="n">
         <v>9406</v>
@@ -1516,7 +1508,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1529,19 +1521,24 @@
           <t>hane</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ovanför Garpedansvägen, Sm</t>
+          <t>Gamleby,, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583523</v>
+        <v>583548</v>
       </c>
       <c r="R9" t="n">
-        <v>6418623</v>
+        <v>6418595</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,17 +1562,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
+          <t>2008-07-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-06-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ekoxeuppropet 2020. 1 levande stillasittande och 2 döda uppätna bakkroppar</t>
+          <t>2008-07-27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,28 +1582,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Ekoxeuppropet 2020</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98324354</t>
+          <t>https://artportalen.se/Sighting/13582134</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>98325197</v>
+        <v>98324657</v>
       </c>
       <c r="B10" t="n">
         <v>9406</v>
@@ -1641,7 +1629,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1649,24 +1637,19 @@
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>garpedansv 1, gamleby, Sm</t>
+          <t>Garpedansvägen 15, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583274</v>
+        <v>583554</v>
       </c>
       <c r="R10" t="n">
-        <v>6418585</v>
+        <v>6418590</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1690,17 +1673,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-06-26</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-06-26</t>
+          <t>2020-06-20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ekoxeuppropet 2020. pigg</t>
+          <t>Ekoxeuppropet 2020. 1 levande resten döende</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,13 +1713,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98325197</t>
+          <t>https://artportalen.se/Sighting/98324657</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>98326116</v>
+        <v>98324354</v>
       </c>
       <c r="B11" t="n">
         <v>9406</v>
@@ -1766,7 +1749,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1776,22 +1759,22 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>garpedansvägen 5, Sm</t>
+          <t>Ovanför Garpedansvägen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583332</v>
+        <v>583523</v>
       </c>
       <c r="R11" t="n">
-        <v>6418576</v>
+        <v>6418623</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,17 +1798,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-06-22</t>
+          <t>2020-06-05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ekoxeuppropet 2020. levande, döda</t>
+          <t>Ekoxeuppropet 2020. 1 levande stillasittande och 2 döda uppätna bakkroppar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,38 +1838,38 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98326116</t>
+          <t>https://artportalen.se/Sighting/98324354</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13582135</v>
+        <v>98325197</v>
       </c>
       <c r="B12" t="n">
-        <v>5495</v>
+        <v>9406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101410</v>
+        <v>101246</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1894,21 +1877,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gamleby,, Sm</t>
+          <t>garpedansv 1, gamleby, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583548</v>
+        <v>583274</v>
       </c>
       <c r="R12" t="n">
-        <v>6418595</v>
+        <v>6418585</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1935,12 +1923,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2008-07-27</t>
+          <t>2020-06-26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2008-07-27</t>
+          <t>2020-06-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020. pigg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,53 +1944,52 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal tall i trädgård</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/13582135</t>
+          <t>https://artportalen.se/Sighting/98325197</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14832018</v>
+        <v>98326116</v>
       </c>
       <c r="B13" t="n">
-        <v>43518</v>
+        <v>9406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101509</v>
+        <v>101246</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Apollofjäril</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parnassius apollo</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2007,7 +1999,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2017,32 +2009,22 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gamleby,, Sm</t>
+          <t>garpedansvägen 5, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583548</v>
+        <v>583332</v>
       </c>
       <c r="R13" t="n">
-        <v>6418595</v>
+        <v>6418576</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2066,12 +2048,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2011-06-26</t>
+          <t>2020-06-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2011-07-09</t>
+          <t>2020-06-22</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020. levande, döda</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,49 +2073,53 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Henriksson</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Via Jan Henriksson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Monika Sunhede</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ekoxeuppropet 2020</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/14832018</t>
+          <t>https://artportalen.se/Sighting/98326116</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127896805</v>
+        <v>13582135</v>
       </c>
       <c r="B14" t="n">
-        <v>56845</v>
+        <v>5495</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100053</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2136,24 +2127,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blåsippevägen, 594 31 Gamleby, Sm</t>
+          <t>Gamleby,, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>582987</v>
+        <v>583548</v>
       </c>
       <c r="R14" t="n">
-        <v>6417401</v>
+        <v>6418595</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2177,22 +2168,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2008-07-27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2008-07-27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,77 +2184,98 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal tall i trädgård</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Via Johan Möller</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127896805</t>
+          <t>https://artportalen.se/Sighting/13582135</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129812725</v>
+        <v>14832018</v>
       </c>
       <c r="B15" t="n">
-        <v>106812</v>
+        <v>43518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220785</v>
+        <v>101509</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gamleby Västervik Kalmar, Sm</t>
+          <t>Gamleby,, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583841</v>
+        <v>583548</v>
       </c>
       <c r="R15" t="n">
-        <v>6417093</v>
+        <v>6418595</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2295,19 +2297,14 @@
           <t>Gamleby</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>057eecec-a8f2-4c79-88bd-2393cd4ba94e</t>
-        </is>
-      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2011-06-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2011-07-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,53 +2319,49 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Torbjörn Blixt</t>
+          <t>Jan Henriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karolina Janiec</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Via Jan Henriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129812725</t>
+          <t>https://artportalen.se/Sighting/14832018</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129812726</v>
+        <v>127896805</v>
       </c>
       <c r="B16" t="n">
-        <v>106812</v>
+        <v>56845</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220785</v>
+        <v>100053</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2376,19 +2369,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gamleby Västervik Kalmar, Sm</t>
+          <t>Blåsippevägen, 594 31 Gamleby, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583841</v>
+        <v>582987</v>
       </c>
       <c r="R16" t="n">
-        <v>6417084</v>
+        <v>6417401</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2410,19 +2408,24 @@
           <t>Gamleby</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>95e877b4-0ba2-4dd9-bd4b-c9ce33b04b23</t>
-        </is>
-      </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2437,28 +2440,28 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Torbjörn Blixt</t>
+          <t>Johan Möller</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karolina Janiec</t>
+          <t>Via Johan Möller</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129812726</t>
+          <t>https://artportalen.se/Sighting/127896805</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129812727</v>
+        <v>129812725</v>
       </c>
       <c r="B17" t="n">
         <v>106812</v>
@@ -2497,10 +2500,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583802</v>
+        <v>583841</v>
       </c>
       <c r="R17" t="n">
-        <v>6417105</v>
+        <v>6417093</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2527,7 +2530,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>1b423e9f-b25f-4888-9c10-e3a7bffe23c3</t>
+          <t>057eecec-a8f2-4c79-88bd-2393cd4ba94e</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2567,13 +2570,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129812727</t>
+          <t>https://artportalen.se/Sighting/129812725</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129812733</v>
+        <v>129812726</v>
       </c>
       <c r="B18" t="n">
         <v>106812</v>
@@ -2612,10 +2615,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583825</v>
+        <v>583841</v>
       </c>
       <c r="R18" t="n">
-        <v>6417068</v>
+        <v>6417084</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2642,7 +2645,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>e32bafc8-b861-4268-bf83-fc7a31a31d8c</t>
+          <t>95e877b4-0ba2-4dd9-bd4b-c9ce33b04b23</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2682,13 +2685,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129812733</t>
+          <t>https://artportalen.se/Sighting/129812726</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129812734</v>
+        <v>129812727</v>
       </c>
       <c r="B19" t="n">
         <v>106812</v>
@@ -2727,10 +2730,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583844</v>
+        <v>583802</v>
       </c>
       <c r="R19" t="n">
-        <v>6417069</v>
+        <v>6417105</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2757,7 +2760,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>b452fe85-46bc-4dea-9334-2ddb83d48cb4</t>
+          <t>1b423e9f-b25f-4888-9c10-e3a7bffe23c3</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2796,6 +2799,236 @@
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129812727</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129812733</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gamleby Västervik Kalmar, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583825</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6417068</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>e32bafc8-b861-4268-bf83-fc7a31a31d8c</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karolina Janiec</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129812733</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129812734</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gamleby Västervik Kalmar, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583844</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6417069</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gamleby</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>b452fe85-46bc-4dea-9334-2ddb83d48cb4</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karolina Janiec</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129812734</t>
         </is>
@@ -2821,6 +3054,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92132</v>
+        <v>92134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/S 1519-2023 artfynd.xlsx
+++ b/artfynd/S 1519-2023 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>136684905</v>
       </c>
       <c r="B3" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136685543</v>
       </c>
       <c r="B4" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
